--- a/feedback_forms/018_epic_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/018_epic_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,8 +596,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,12 +625,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'question_1',_'label':_'what_did_you_enjoy_most_about_the_service?',_'type':_'text'}</t>
+          <t>what_did_you_enjoy_most_about_the_service?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'question_1', 'label': 'What did you enjoy most about the service?', 'type': 'text'}</t>
+          <t>What did you enjoy most about the service?</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'question_2',_'label':_'what_did_you_enjoy_least_about_the_service?',_'type':_'text'}</t>
+          <t>what_did_you_enjoy_least_about_the_service?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'question_2', 'label': 'What did you enjoy least about the service?', 'type': 'text'}</t>
+          <t>What did you enjoy least about the service?</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'question_3',_'label':_'how_likely_are_you_to_recommend_the_service?',_'type':_'select_one',_'options':_[{'id':_7,_'name':_'not_at_all_likely',_'label':_'not_at_all_likely'},_{'id':_8,_'name':_'somewhat_likely',_'label':_'somewhat_likely'},_{'id':_9,_'name':_'very_likely',_'label':_'very_likely'},_{'id':_10,_'name':_'extremely_likely',_'label':_'extremely_likely'}]}</t>
+          <t>how_likely_are_you_to_recommend_the_service?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'question_3', 'label': 'How likely are you to recommend the service?', 'type': 'select_one', 'options': [{'id': 7, 'name': 'Not at all likely', 'label': 'Not at all likely'}, {'id': 8, 'name': 'Somewhat likely', 'label': 'Somewhat likely'}, {'id': 9, 'name': 'Very likely', 'label': 'Very likely'}, {'id': 10, 'name': 'Extremely likely', 'label': 'Extremely likely'}]}</t>
+          <t>How likely are you to recommend the service?</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'comments',_'label':_'comments',_'type':_'text',_'hint':_none,_'options':_[]}</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'comments', 'label': 'Comments', 'type': 'text', 'hint': None, 'options': []}</t>
+          <t>Comments</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'contact_info',_'label':_'contact_info',_'type':_'text',_'hint':_none,_'options':_[]}</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'contact_info', 'label': 'Contact Info', 'type': 'text', 'hint': None, 'options': []}</t>
+          <t>Contact Info</t>
         </is>
       </c>
     </row>
